--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80954C4-EE78-4AAE-8105-20C8F406F975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588D0974-EB45-4BB3-95B6-F670995C47BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="pricing-calculator" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Product Name</t>
   </si>
@@ -120,6 +120,24 @@
   </si>
   <si>
     <t>Ideal Profit</t>
+  </si>
+  <si>
+    <t>Dove</t>
+  </si>
+  <si>
+    <t>Trinity</t>
+  </si>
+  <si>
+    <t>Halo</t>
+  </si>
+  <si>
+    <t>Sundrop</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>Loveknot</t>
   </si>
 </sst>
 </file>
@@ -988,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -1807,6 +1825,276 @@
         <v>₹2,999</v>
       </c>
     </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19">
+        <v>450</v>
+      </c>
+      <c r="C19">
+        <v>50</v>
+      </c>
+      <c r="D19">
+        <v>150</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ref="E19" si="13">B19+C19+D19</f>
+        <v>650</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ref="G19" si="14">ROUNDUP((E19*F19)/500,0)*500-1</f>
+        <v>1499</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ref="H19" si="15">G19*2%</f>
+        <v>29.98</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ref="I19" si="16">G19-H19</f>
+        <v>1469.02</v>
+      </c>
+      <c r="J19">
+        <f t="shared" ref="J19" si="17">I19-E19</f>
+        <v>819.02</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" ref="K19" si="18">J19/G19</f>
+        <v>0.54637758505670442</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" ref="L19" si="19">"₹"&amp;TEXT(G19,"#,##0")</f>
+        <v>₹1,499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>130</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>150</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20" si="20">B20+C20+D20</f>
+        <v>330</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ref="G20" si="21">ROUNDUP((E20*F20)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H20" si="22">G20*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ref="I20" si="23">G20-H20</f>
+        <v>979.02</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ref="J20" si="24">I20-E20</f>
+        <v>649.02</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" ref="K20" si="25">J20/G20</f>
+        <v>0.64966966966966966</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" ref="L20" si="26">"₹"&amp;TEXT(G20,"#,##0")</f>
+        <v>₹999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>145</v>
+      </c>
+      <c r="C21">
+        <v>50</v>
+      </c>
+      <c r="D21">
+        <v>150</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ref="E21" si="27">B21+C21+D21</f>
+        <v>345</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ref="G21" si="28">ROUNDUP((E21*F21)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ref="H21" si="29">G21*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ref="I21" si="30">G21-H21</f>
+        <v>979.02</v>
+      </c>
+      <c r="J21">
+        <f t="shared" ref="J21" si="31">I21-E21</f>
+        <v>634.02</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" ref="K21" si="32">J21/G21</f>
+        <v>0.63465465465465465</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" ref="L21" si="33">"₹"&amp;TEXT(G21,"#,##0")</f>
+        <v>₹999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22">
+        <v>480</v>
+      </c>
+      <c r="C22">
+        <v>50</v>
+      </c>
+      <c r="D22">
+        <v>150</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ref="E22" si="34">B22+C22+D22</f>
+        <v>680</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <f t="shared" ref="G22" si="35">ROUNDUP((E22*F22)/500,0)*500-1</f>
+        <v>1499</v>
+      </c>
+      <c r="H22">
+        <f t="shared" ref="H22" si="36">G22*2%</f>
+        <v>29.98</v>
+      </c>
+      <c r="I22">
+        <f t="shared" ref="I22" si="37">G22-H22</f>
+        <v>1469.02</v>
+      </c>
+      <c r="J22">
+        <f t="shared" ref="J22" si="38">I22-E22</f>
+        <v>789.02</v>
+      </c>
+      <c r="K22" s="1">
+        <f t="shared" ref="K22" si="39">J22/G22</f>
+        <v>0.52636424282855232</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" ref="L22" si="40">"₹"&amp;TEXT(G22,"#,##0")</f>
+        <v>₹1,499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>130</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23">
+        <v>150</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ref="E23" si="41">B23+C23+D23</f>
+        <v>330</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ref="G23" si="42">ROUNDUP((E23*F23)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H23">
+        <f t="shared" ref="H23" si="43">G23*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ref="I23" si="44">G23-H23</f>
+        <v>979.02</v>
+      </c>
+      <c r="J23">
+        <f t="shared" ref="J23" si="45">I23-E23</f>
+        <v>649.02</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" ref="K23" si="46">J23/G23</f>
+        <v>0.64966966966966966</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" ref="L23" si="47">"₹"&amp;TEXT(G23,"#,##0")</f>
+        <v>₹999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24">
+        <v>99</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>150</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ref="E24" si="48">B24+C24+D24</f>
+        <v>299</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" ref="G24" si="49">ROUNDUP((E24*F24)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H24">
+        <f t="shared" ref="H24" si="50">G24*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ref="I24" si="51">G24-H24</f>
+        <v>979.02</v>
+      </c>
+      <c r="J24">
+        <f t="shared" ref="J24" si="52">I24-E24</f>
+        <v>680.02</v>
+      </c>
+      <c r="K24" s="1">
+        <f t="shared" ref="K24" si="53">J24/G24</f>
+        <v>0.68070070070070066</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" ref="L24" si="54">"₹"&amp;TEXT(G24,"#,##0")</f>
+        <v>₹999</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L17">
     <sortCondition ref="G2:G17"/>
